--- a/artfynd/A 6327-2026 artfynd.xlsx
+++ b/artfynd/A 6327-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,35 +675,34 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120441511</v>
+        <v>120442565</v>
       </c>
       <c r="B2" t="n">
-        <v>88638</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89111</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4398</v>
+        <v>809</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vit vaxskivling</t>
+          <t>Praktvaxing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cuphophyllus virgineus s.lat.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Hygrocybe splendidissima</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(P.D.Orton) M.M.Moser</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
@@ -716,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>459784</v>
+        <v>459674</v>
       </c>
       <c r="R2" t="n">
-        <v>6419471</v>
+        <v>6419334</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -761,7 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Doft av honung</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,15 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120442489</v>
+        <v>120441488</v>
       </c>
       <c r="B3" t="n">
-        <v>88449</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>88424</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -804,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4377</v>
+        <v>1008</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blodvaxskivling</t>
+          <t>Igelkottsröksvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hygrocybe coccinea</t>
+          <t>Lycoperdon echinatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) P.Kumm.</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -833,13 +832,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>459795</v>
+        <v>459784</v>
       </c>
       <c r="R3" t="n">
-        <v>6419350</v>
+        <v>6419471</v>
       </c>
       <c r="S3" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -868,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -878,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,58 +904,53 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120442565</v>
+        <v>120441463</v>
       </c>
       <c r="B4" t="n">
-        <v>88481</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>809</v>
+        <v>2810</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Praktvaxskivling</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hygrocybe splendidissima</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.D.Orton) M.M.Moser</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>utan kapsel</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Siggarps hagar, Sm</t>
+          <t>Högaberget, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>459674</v>
+        <v>459760</v>
       </c>
       <c r="R4" t="n">
-        <v>6419334</v>
+        <v>6419607</v>
       </c>
       <c r="S4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -985,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -995,12 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:06</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Doft av honung</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,12 +1019,7 @@
         <v>120442506</v>
       </c>
       <c r="B5" t="n">
-        <v>87757</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>88978</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1153,15 +1137,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120441488</v>
+        <v>120442514</v>
       </c>
       <c r="B6" t="n">
-        <v>87238</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89081</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1169,21 +1148,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1008</v>
+        <v>4374</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Igelkottsröksvamp</t>
+          <t>Gulvaxing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycoperdon echinatum</t>
+          <t>Hygrocybe chlorophana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>(Fr.) Wünsche</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1198,13 +1177,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>459784</v>
+        <v>459761</v>
       </c>
       <c r="R6" t="n">
-        <v>6419471</v>
+        <v>6419320</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1233,7 +1212,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1243,7 +1222,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1270,15 +1249,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120442514</v>
+        <v>120442489</v>
       </c>
       <c r="B7" t="n">
-        <v>88447</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89083</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1286,21 +1260,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4374</v>
+        <v>4377</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gul vaxskivling</t>
+          <t>Blodvaxing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hygrocybe chlorophana</t>
+          <t>Hygrocybe coccinea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Wünsche</t>
+          <t>(Schaeff.) P.Kumm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1315,13 +1289,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>459761</v>
+        <v>459795</v>
       </c>
       <c r="R7" t="n">
-        <v>6419320</v>
+        <v>6419350</v>
       </c>
       <c r="S7" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1350,7 +1324,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1360,7 +1334,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1384,6 +1358,240 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>120441511</v>
+      </c>
+      <c r="B8" t="n">
+        <v>89035</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>4398</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vitvaxing agg.</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Cuphophyllus virgineus s.lat.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Siggarps hagar, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>459784</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6419471</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Skärstad</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>120442654</v>
+      </c>
+      <c r="B9" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Högaberget, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>459726</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6419648</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Skärstad</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 6327-2026 artfynd.xlsx
+++ b/artfynd/A 6327-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -789,6 +794,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120442565</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -901,6 +911,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120441488</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1013,6 +1028,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120441463</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1134,6 +1154,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120442506</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1246,6 +1271,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120442514</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1358,6 +1388,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120442489</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1466,6 +1501,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120441511</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1592,8 +1632,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120442654</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>